--- a/data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_kg.xlsx
+++ b/data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_kg.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,7 +1061,7 @@
         <v>46234</v>
       </c>
       <c r="B80" t="n">
-        <v>35002833875</v>
+        <v>34974584205</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,15 @@
         <v>46265</v>
       </c>
       <c r="B81" t="n">
-        <v>34406447895</v>
+        <v>34351503645</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>31660490297</v>
       </c>
     </row>
   </sheetData>
